--- a/合同全生命周期管理系统-项目管理套件/09_上线移交与运营/上线移交与运营-20260918-V5.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/09_上线移交与运营/上线移交与运营-20260918-V5.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="12700" firstSheet="4" activeTab="9"/>
+    <workbookView windowWidth="28260" windowHeight="12700" firstSheet="4" activeTab="0"/>
   </bookViews>
   <sheets>
+    <sheet name="使用说明" sheetId="2" r:id="rId2"/>
     <sheet name="上线总览" sheetId="1" r:id="rId1"/>
-    <sheet name="使用说明" sheetId="2" r:id="rId2"/>
     <sheet name="上线策略" sheetId="3" r:id="rId3"/>
     <sheet name="上线准备清单" sheetId="4" r:id="rId4"/>
     <sheet name="数据迁移与核验" sheetId="5" r:id="rId5"/>
